--- a/output/masters-research.xlsx
+++ b/output/masters-research.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="588">
   <si>
     <t xml:space="preserve">European Master's Research — Results</t>
   </si>
@@ -73,19 +73,22 @@
     <t xml:space="preserve">   Tunisian law fixes the licence at 180 credits. Confirm you hold the diploma.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Your binding constraint is that you have no English test. Four separate lines of</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   research reached this conclusion. Book IELTS in Sousse (~700 TND). There is no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   waiver open to you.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Tuition is often not the real cost. France now requires ~EUR 14,500 demonstrated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   for a year-one visa; Norway ~EUR 14,600. Check the visa funds column.</t>
+    <t xml:space="preserve">2. You do NOT need an English test to apply everywhere. Three programmes take you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   with no certificate at all: EUBA Bratislava (free, AACSB), Corvinus Budapest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   (triple-accredited) and Bergamo. Sit IELTS anyway - it opens far more doors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Tuition is rarely the real cost. The visa deposit is: France ~EUR 14,500,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Norway ~EUR 14,600, Germany EUR 11,904. Check the visa funds column - Norway is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   effectively closed because no Norwegian institution offers a grant to satisfy it.</t>
   </si>
   <si>
     <t xml:space="preserve">A NOTE ON ACCURACY</t>
@@ -154,6 +157,84 @@
     <t xml:space="preserve">146 verdict</t>
   </si>
   <si>
+    <t xml:space="preserve">MSc Marketing and Trade Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUBA Bratislava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovakia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bratislava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D1/D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA International Marketing Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HWR Berlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corvinus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Marketing (Stipendium-funded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIOCA - Innovation &amp; Organization of Culture and the Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universita di Bologna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bologna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Digital Customer Experience &amp; Service Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KU Eichstatt-Ingolstadt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingolstadt</t>
+  </si>
+  <si>
     <t xml:space="preserve">MA Digital Marketing</t>
   </si>
   <si>
@@ -169,115 +250,589 @@
     <t xml:space="preserve">D2</t>
   </si>
   <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY OK</t>
-  </si>
-  <si>
     <t xml:space="preserve">MA Data Science &amp; Intelligent Analytics</t>
   </si>
   <si>
-    <t xml:space="preserve">D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIOCA — Innovation &amp; Organization of Culture and the Arts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universita di Bologna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bologna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1 Management de l'innovation -&gt; M2 Ecosysteme de la Musique</t>
+    <t xml:space="preserve">Marketing and Global Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milano-Bicocca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universita di Pavia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universita di Bergamo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bergamo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master MMX - Marketing et Management de l Experience Client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Gustave Eiffel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marne-la-Vallee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Marketing-Vente (M1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iaelyon / Lyon 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 Marketing (formation initiale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGR-IAE Rennes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rennes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-Marketing et Strategie Digitale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EM Strasbourg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strasbourg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 Mgmt innovation -&gt; M2 Ecosysteme de la Musique</t>
   </si>
   <si>
     <t xml:space="preserve">Universite Lumiere Lyon 2</t>
   </si>
   <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyon</t>
-  </si>
-  <si>
     <t xml:space="preserve">D3</t>
   </si>
   <si>
-    <t xml:space="preserve">French</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master Marketing-Vente (M1 entry)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iaelyon / Lyon 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1 Marketing (formation initiale)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IGR-IAE Rennes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rennes</t>
+    <t xml:space="preserve">Master 120 publicite et communication commerciale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IHECS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brussels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORDERLINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master en gestion de l entreprise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICHEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR/EN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master 120 sciences de gestion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMons Warocque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Economics &amp; Business Admin (Business Data Science)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aalborg University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aalborg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Business (MA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uniwersytet Warszawski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warsaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data-Driven Marketing, Digital Marketing &amp; Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOVA IMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA Innovation and Technology Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Tartu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tartu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA Digital Marketing Communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Malta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Msida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Customer Relationship Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASE Bucharest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucharest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UTB Zlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Artificial Intelligence (net of automatic award)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTU Cork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direccion de Marketing Digital y Social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universidad de Cadiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direccion y Gestion de Marketing Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universidad de Malaga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malaga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direzione d Impresa, Marketing e Strategia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universita di Torino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Popular Music: Music Business and Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universitetet i Agder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kristiansand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master in Digital Transformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kongsberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDSI - Service Design Strategies &amp; Innovations (if funded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erasmus Mundus consortium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FI/LV/EE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">various</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow cells: no official cost-of-living figure was found. Enter your own estimate and the total will calculate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"EST. TOTAL" shows tuition only where living cost is blank. Visa funds are additional and must be demonstrated, not spent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bologna assumes an ISEE parificato under EUR 27,000. Without it a different non-EU fee schedule applies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDSI shown at zero assuming an Erasmus Mundus scholarship; unfunded it is EUR 8,000/yr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All programmes found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master's degrees only. Certificates, titulos propios and Italian Master di I livello are on the "Excluded" sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuition (EUR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entry / 146 verdict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D1 AI/data marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">727/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK — 30 ECTS business subjects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free prep course for maths prerequisite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data-Driven Marketing, Digital Mktg &amp; Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,500 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/28 applications open soon</t>
   </si>
   <si>
     <t xml:space="preserve">MSc Econ &amp; Business Admin (Business Data Science)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aalborg University</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denmark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aalborg</t>
+    <t xml:space="preserve">7,450/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~15 fully funded awards, automatic consideration</t>
   </si>
   <si>
     <t xml:space="preserve">International Business</t>
   </si>
   <si>
-    <t xml:space="preserve">Universitetet i Agder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kristiansand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data-Driven Marketing, Digital Marketing &amp; Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOVA IMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portugal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital Business (MA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uniwersytet Warszawski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warsaw</t>
+    <t xml:space="preserve">5,385/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK — assessed by years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest verified tuition in report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business &amp; Digital Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uniwersytet Lodzki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,500/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Analytics / Big Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGH Warsaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,600/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland's leading business school</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic Data Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VSE Prague</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,000/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Strategic Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULiege / HEC Liege</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French/English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,369/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publishes a minimum 12/20 average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Artificial Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,000 net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORDERLINE — wants NFQ L8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatic EUR 2,500 award</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Business Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATU Sligo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,000/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published RPL route</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Driven Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUAS Amsterdam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,648/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPENDS on licence type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if Licence Appliquee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Marketing and Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UEF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~7,000 net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True D1+D2 hybrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing y Comportamiento del Consumidor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGR / UJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1,300 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andalucia rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marqueting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAB Barcelona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish/Catalan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalonia rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2 Digital marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK — no 180 ECTS rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOP PICK. Deadline 3 Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2 English via free in-house test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~2,700/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entry names marketing as qualifying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCURI (customer relationship marketing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UE Katowice + 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,150 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Literally demands 180 ECTS. Closest to his CRM project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,055/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trains "specialistes de la relation client"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formation initiale only — no alternance trap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc 1 Management -&gt; MSc 2 Marketing &amp; Brand Mgmt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Aix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,400 / 2yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admits bac+3 "or credits" — best wording found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entry test has no eliminating minimum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grenoble IAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three digital M2 exits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 e-Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Montpellier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free public transport in city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Strategic Digital Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">York St John</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBP 11,800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK — no ECTS rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">February intake available</t>
   </si>
   <si>
     <t xml:space="preserve">Master en gestion de l'entreprise</t>
@@ -286,375 +841,6 @@
     <t xml:space="preserve">ICHEC Brussels</t>
   </si>
   <si>
-    <t xml:space="preserve">Belgium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brussels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">French/English</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BORDERLINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Strategic Marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULiege / HEC Liege</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liege</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc Artificial Intelligence (net of automatic award)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTU Cork</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ireland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cork</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direccion y Gestion de Marketing Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universidad de Malaga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malaga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spanish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Popular Music: Music Business and Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDSI — Service Design Strategies &amp; Innovations (if funded)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erasmus Mundus consortium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FI/LV/EE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">various</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D1/D2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow cells: no official cost-of-living figure was found. Enter your own estimate and the total will calculate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"EST. TOTAL" shows tuition only where living cost is blank. Visa funds are additional and must be demonstrated, not spent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bologna assumes an ISEE parificato under EUR 27,000. Without it a different non-EU fee schedule applies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDSI shown at zero assuming an Erasmus Mundus scholarship; unfunded it is EUR 8,000/yr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All programmes found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master's degrees only. Certificates, titulos propios and Italian Master di I livello are on the "Excluded" sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuition (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entry / 146 verdict</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D1 AI/data marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">727/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY OK — 30 ECTS business subjects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free prep course for maths prerequisite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data-Driven Marketing, Digital Mktg &amp; Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,500 total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/28 applications open soon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,450/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~15 fully funded awards, automatic consideration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,385/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY OK — assessed by years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheapest verified tuition in report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business &amp; Digital Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uniwersytet Lodzki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,500/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Analytics / Big Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGH Warsaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,600/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland's leading business school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Economic Data Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VSE Prague</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,000/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,369/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publishes a minimum 12/20 average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc Artificial Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11,000 net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BORDERLINE — wants NFQ L8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatic EUR 2,500 award</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc Business Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATU Sligo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,000/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Published RPL route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital Driven Business</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUAS Amsterdam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netherlands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,648/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEPENDS on licence type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only if Licence Appliquee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital Marketing and Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UEF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~7,000 net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">True D1+D2 hybrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketing y Comportamiento del Consumidor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UGR / UJA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~1,300 total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andalucia rates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marqueting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UAB Barcelona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spanish/Catalan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalonia rates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2 Digital marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY OK — no 180 ECTS rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOP PICK. Deadline 3 Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B2 English via free in-house test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketing Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UTB Zlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~2,700/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entry names marketing as qualifying</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MERCURI (customer relationship marketing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UE Katowice + 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,150 total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Literally demands 180 ECTS. Closest to his CRM project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master Marketing-Vente (M1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,055/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trains "specialistes de la relation client"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1 Marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formation initiale only — no alternance trap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc 1 Management -&gt; MSc 2 Marketing &amp; Brand Mgmt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAE Aix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,400 / 2yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admits bac+3 "or credits" — best wording found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketing Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAE Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entry test has no eliminating minimum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenoble IAE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Three digital M2 exits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1 e-Marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAE Montpellier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free public transport in city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc Strategic Digital Marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">York St John</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBP 11,800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY OK — no ECTS rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">February intake available</t>
-  </si>
-  <si>
     <t xml:space="preserve">Private</t>
   </si>
   <si>
@@ -688,9 +874,6 @@
     <t xml:space="preserve">UNIMORE Reggio Emilia</t>
   </si>
   <si>
-    <t xml:space="preserve">Italian</t>
-  </si>
-  <si>
     <t xml:space="preserve">Open admission — only 30 ECTS bar</t>
   </si>
   <si>
@@ -724,9 +907,6 @@
     <t xml:space="preserve">D3 Music marketing</t>
   </si>
   <si>
-    <t xml:space="preserve">M1 Mgmt innovation -&gt; M2 Ecosysteme de la Musique</t>
-  </si>
-  <si>
     <t xml:space="preserve">Best route in this direction. M1 entry from L3 gestion</t>
   </si>
   <si>
@@ -973,9 +1153,6 @@
     <t xml:space="preserve">Fair</t>
   </si>
   <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
     <t xml:space="preserve">0 + stipend if funded</t>
   </si>
   <si>
@@ -1016,9 +1193,6 @@
   </si>
   <si>
     <t xml:space="preserve">Funding closed to Tunisians</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
   </si>
   <si>
     <t xml:space="preserve">~0-1,500</t>
@@ -1803,15 +1977,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2083,7 +2257,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="95"/>
@@ -2220,20 +2394,20 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
+      <c r="A33" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="A34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
@@ -2243,6 +2417,11 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2261,7 +2440,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2282,62 +2461,62 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2345,48 +2524,50 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>727</v>
+        <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="11" t="n">
+      <c r="K5" s="9" t="n">
+        <v>490</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <f aca="false">I5*J5</f>
-        <v>1454</v>
-      </c>
-      <c r="M5" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="M5" s="10" t="n">
         <f aca="false">IF(K5="","",K5*12*J5)</f>
-        <v/>
-      </c>
-      <c r="N5" s="12" t="n">
+        <v>11760</v>
+      </c>
+      <c r="N5" s="11" t="n">
         <f aca="false">IF(K5="",L5,L5+M5)</f>
-        <v>1454</v>
+        <v>11760</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2394,48 +2575,50 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>727</v>
+        <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="11" t="n">
+      <c r="K6" s="12"/>
+      <c r="L6" s="10" t="n">
         <f aca="false">I6*J6</f>
-        <v>1454</v>
-      </c>
-      <c r="M6" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="M6" s="10" t="str">
         <f aca="false">IF(K6="","",K6*12*J6)</f>
         <v/>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" s="11" t="n">
         <f aca="false">IF(K6="",L6,L6+M6)</f>
-        <v>1454</v>
-      </c>
-      <c r="O6" s="8"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>11904</v>
+      </c>
       <c r="P6" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2443,48 +2626,50 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>157</v>
+        <v>7400</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="11" t="n">
+      <c r="K7" s="9" t="n">
+        <v>700</v>
+      </c>
+      <c r="L7" s="10" t="n">
         <f aca="false">I7*J7</f>
-        <v>314</v>
-      </c>
-      <c r="M7" s="11" t="str">
+        <v>14800</v>
+      </c>
+      <c r="M7" s="10" t="n">
         <f aca="false">IF(K7="","",K7*12*J7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="12" t="n">
+        <v>16800</v>
+      </c>
+      <c r="N7" s="11" t="n">
         <f aca="false">IF(K7="",L7,L7+M7)</f>
-        <v>314</v>
+        <v>31600</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2492,52 +2677,50 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="G8" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>4055</v>
+        <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>2</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>1324</v>
-      </c>
-      <c r="L8" s="11" t="n">
+        <v>700</v>
+      </c>
+      <c r="L8" s="10" t="n">
         <f aca="false">I8*J8</f>
-        <v>8110</v>
-      </c>
-      <c r="M8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10" t="n">
         <f aca="false">IF(K8="","",K8*12*J8)</f>
-        <v>31776</v>
-      </c>
-      <c r="N8" s="12" t="n">
+        <v>16800</v>
+      </c>
+      <c r="N8" s="11" t="n">
         <f aca="false">IF(K8="",L8,L8+M8)</f>
-        <v>39886</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>14500</v>
-      </c>
+        <v>16800</v>
+      </c>
+      <c r="O8" s="8"/>
       <c r="P8" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2545,52 +2728,48 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="F9" s="6" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>4055</v>
+        <v>157</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" s="9" t="n">
-        <v>1324</v>
-      </c>
-      <c r="L9" s="11" t="n">
+      <c r="K9" s="12"/>
+      <c r="L9" s="10" t="n">
         <f aca="false">I9*J9</f>
-        <v>8110</v>
-      </c>
-      <c r="M9" s="11" t="n">
+        <v>314</v>
+      </c>
+      <c r="M9" s="10" t="str">
         <f aca="false">IF(K9="","",K9*12*J9)</f>
-        <v>31776</v>
-      </c>
-      <c r="N9" s="12" t="n">
+        <v/>
+      </c>
+      <c r="N9" s="11" t="n">
         <f aca="false">IF(K9="",L9,L9+M9)</f>
-        <v>39886</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>14500</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="O9" s="8"/>
       <c r="P9" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2598,52 +2777,50 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>4055</v>
+        <v>176</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="9" t="n">
-        <v>1192</v>
-      </c>
-      <c r="L10" s="11" t="n">
+      <c r="K10" s="12"/>
+      <c r="L10" s="10" t="n">
         <f aca="false">I10*J10</f>
-        <v>8110</v>
-      </c>
-      <c r="M10" s="11" t="n">
+        <v>352</v>
+      </c>
+      <c r="M10" s="10" t="str">
         <f aca="false">IF(K10="","",K10*12*J10)</f>
-        <v>28608</v>
-      </c>
-      <c r="N10" s="12" t="n">
+        <v/>
+      </c>
+      <c r="N10" s="11" t="n">
         <f aca="false">IF(K10="",L10,L10+M10)</f>
-        <v>36718</v>
+        <v>352</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>14500</v>
+        <v>11904</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2651,48 +2828,48 @@
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>7450</v>
+        <v>727</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="11" t="n">
+      <c r="K11" s="12"/>
+      <c r="L11" s="10" t="n">
         <f aca="false">I11*J11</f>
-        <v>14900</v>
-      </c>
-      <c r="M11" s="11" t="str">
+        <v>1454</v>
+      </c>
+      <c r="M11" s="10" t="str">
         <f aca="false">IF(K11="","",K11*12*J11)</f>
         <v/>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="N11" s="11" t="n">
         <f aca="false">IF(K11="",L11,L11+M11)</f>
-        <v>14900</v>
+        <v>1454</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2700,50 +2877,48 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="F12" s="6" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>5385</v>
+        <v>727</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="11" t="n">
+      <c r="K12" s="12"/>
+      <c r="L12" s="10" t="n">
         <f aca="false">I12*J12</f>
-        <v>10770</v>
-      </c>
-      <c r="M12" s="11" t="str">
+        <v>1454</v>
+      </c>
+      <c r="M12" s="10" t="str">
         <f aca="false">IF(K12="","",K12*12*J12)</f>
         <v/>
       </c>
-      <c r="N12" s="12" t="n">
+      <c r="N12" s="11" t="n">
         <f aca="false">IF(K12="",L12,L12+M12)</f>
-        <v>10770</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>14600</v>
-      </c>
+        <v>1454</v>
+      </c>
+      <c r="O12" s="8"/>
       <c r="P12" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2751,48 +2926,48 @@
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="F13" s="6" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>3750</v>
+        <v>346</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="11" t="n">
+      <c r="K13" s="12"/>
+      <c r="L13" s="10" t="n">
         <f aca="false">I13*J13</f>
-        <v>7500</v>
-      </c>
-      <c r="M13" s="11" t="str">
+        <v>692</v>
+      </c>
+      <c r="M13" s="10" t="str">
         <f aca="false">IF(K13="","",K13*12*J13)</f>
         <v/>
       </c>
-      <c r="N13" s="12" t="n">
+      <c r="N13" s="11" t="n">
         <f aca="false">IF(K13="",L13,L13+M13)</f>
-        <v>7500</v>
+        <v>692</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2800,48 +2975,48 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="F14" s="6" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>5000</v>
+        <v>390</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="12"/>
+      <c r="L14" s="10" t="n">
         <f aca="false">I14*J14</f>
-        <v>7500</v>
-      </c>
-      <c r="M14" s="11" t="str">
+        <v>780</v>
+      </c>
+      <c r="M14" s="10" t="str">
         <f aca="false">IF(K14="","",K14*12*J14)</f>
         <v/>
       </c>
-      <c r="N14" s="12" t="n">
+      <c r="N14" s="11" t="n">
         <f aca="false">IF(K14="",L14,L14+M14)</f>
-        <v>7500</v>
+        <v>780</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2849,48 +3024,48 @@
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>5369</v>
+        <v>400</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="11" t="n">
+      <c r="K15" s="12"/>
+      <c r="L15" s="10" t="n">
         <f aca="false">I15*J15</f>
-        <v>10738</v>
-      </c>
-      <c r="M15" s="11" t="str">
+        <v>800</v>
+      </c>
+      <c r="M15" s="10" t="str">
         <f aca="false">IF(K15="","",K15*12*J15)</f>
         <v/>
       </c>
-      <c r="N15" s="12" t="n">
+      <c r="N15" s="11" t="n">
         <f aca="false">IF(K15="",L15,L15+M15)</f>
-        <v>10738</v>
+        <v>800</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="6" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2898,48 +3073,52 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>86</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>88</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>5369</v>
+        <v>4055</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="11" t="n">
+      <c r="K16" s="9" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L16" s="10" t="n">
         <f aca="false">I16*J16</f>
-        <v>10738</v>
-      </c>
-      <c r="M16" s="11" t="str">
+        <v>8110</v>
+      </c>
+      <c r="M16" s="10" t="n">
         <f aca="false">IF(K16="","",K16*12*J16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N16" s="11" t="n">
         <f aca="false">IF(K16="",L16,L16+M16)</f>
-        <v>10738</v>
-      </c>
-      <c r="O16" s="8"/>
+        <v>38110</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>14500</v>
+      </c>
       <c r="P16" s="6" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2947,48 +3126,52 @@
         <v>13</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>11000</v>
+        <v>4055</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>1324</v>
+      </c>
+      <c r="L17" s="10" t="n">
         <f aca="false">I17*J17</f>
-        <v>11000</v>
-      </c>
-      <c r="M17" s="11" t="str">
+        <v>8110</v>
+      </c>
+      <c r="M17" s="10" t="n">
         <f aca="false">IF(K17="","",K17*12*J17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="12" t="n">
+        <v>31776</v>
+      </c>
+      <c r="N17" s="11" t="n">
         <f aca="false">IF(K17="",L17,L17+M17)</f>
-        <v>11000</v>
-      </c>
-      <c r="O17" s="8"/>
+        <v>39886</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>14500</v>
+      </c>
       <c r="P17" s="6" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,48 +3179,52 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>864</v>
+        <v>4055</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>1192</v>
+      </c>
+      <c r="L18" s="10" t="n">
         <f aca="false">I18*J18</f>
-        <v>1296</v>
-      </c>
-      <c r="M18" s="11" t="str">
+        <v>8110</v>
+      </c>
+      <c r="M18" s="10" t="n">
         <f aca="false">IF(K18="","",K18*12*J18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="12" t="n">
+        <v>28608</v>
+      </c>
+      <c r="N18" s="11" t="n">
         <f aca="false">IF(K18="",L18,L18+M18)</f>
-        <v>1296</v>
-      </c>
-      <c r="O18" s="8"/>
+        <v>36718</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>14500</v>
+      </c>
       <c r="P18" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3045,50 +3232,50 @@
         <v>15</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="G19" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>11540</v>
+        <v>4055</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="11" t="n">
+      <c r="K19" s="12"/>
+      <c r="L19" s="10" t="n">
         <f aca="false">I19*J19</f>
-        <v>23080</v>
-      </c>
-      <c r="M19" s="11" t="str">
+        <v>8110</v>
+      </c>
+      <c r="M19" s="10" t="str">
         <f aca="false">IF(K19="","",K19*12*J19)</f>
         <v/>
       </c>
-      <c r="N19" s="12" t="n">
+      <c r="N19" s="11" t="n">
         <f aca="false">IF(K19="",L19,L19+M19)</f>
-        <v>23080</v>
+        <v>8110</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>14600</v>
+        <v>14500</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3096,68 +3283,909 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0</v>
+        <v>4055</v>
       </c>
       <c r="J20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="11" t="n">
+      <c r="K20" s="9" t="n">
+        <v>1324</v>
+      </c>
+      <c r="L20" s="10" t="n">
         <f aca="false">I20*J20</f>
+        <v>8110</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <f aca="false">IF(K20="","",K20*12*J20)</f>
+        <v>31776</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <f aca="false">IF(K20="",L20,L20+M20)</f>
+        <v>39886</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>14500</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>5369</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="12"/>
+      <c r="L21" s="10" t="n">
+        <f aca="false">I21*J21</f>
+        <v>10738</v>
+      </c>
+      <c r="M21" s="10" t="str">
+        <f aca="false">IF(K21="","",K21*12*J21)</f>
+        <v/>
+      </c>
+      <c r="N21" s="11" t="n">
+        <f aca="false">IF(K21="",L21,L21+M21)</f>
+        <v>10738</v>
+      </c>
+      <c r="O21" s="8"/>
+      <c r="P21" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>5369</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="12"/>
+      <c r="L22" s="10" t="n">
+        <f aca="false">I22*J22</f>
+        <v>10738</v>
+      </c>
+      <c r="M22" s="10" t="str">
+        <f aca="false">IF(K22="","",K22*12*J22)</f>
+        <v/>
+      </c>
+      <c r="N22" s="11" t="n">
+        <f aca="false">IF(K22="",L22,L22+M22)</f>
+        <v>10738</v>
+      </c>
+      <c r="O22" s="8"/>
+      <c r="P22" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>5369</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="12"/>
+      <c r="L23" s="10" t="n">
+        <f aca="false">I23*J23</f>
+        <v>10738</v>
+      </c>
+      <c r="M23" s="10" t="str">
+        <f aca="false">IF(K23="","",K23*12*J23)</f>
+        <v/>
+      </c>
+      <c r="N23" s="11" t="n">
+        <f aca="false">IF(K23="",L23,L23+M23)</f>
+        <v>10738</v>
+      </c>
+      <c r="O23" s="8"/>
+      <c r="P23" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>7450</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="12"/>
+      <c r="L24" s="10" t="n">
+        <f aca="false">I24*J24</f>
+        <v>14900</v>
+      </c>
+      <c r="M24" s="10" t="str">
+        <f aca="false">IF(K24="","",K24*12*J24)</f>
+        <v/>
+      </c>
+      <c r="N24" s="11" t="n">
+        <f aca="false">IF(K24="",L24,L24+M24)</f>
+        <v>14900</v>
+      </c>
+      <c r="O24" s="8"/>
+      <c r="P24" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K25" s="12"/>
+      <c r="L25" s="10" t="n">
+        <f aca="false">I25*J25</f>
+        <v>7500</v>
+      </c>
+      <c r="M25" s="10" t="str">
+        <f aca="false">IF(K25="","",K25*12*J25)</f>
+        <v/>
+      </c>
+      <c r="N25" s="11" t="n">
+        <f aca="false">IF(K25="",L25,L25+M25)</f>
+        <v>7500</v>
+      </c>
+      <c r="O25" s="8"/>
+      <c r="P25" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>3750</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="12"/>
+      <c r="L26" s="10" t="n">
+        <f aca="false">I26*J26</f>
+        <v>7500</v>
+      </c>
+      <c r="M26" s="10" t="str">
+        <f aca="false">IF(K26="","",K26*12*J26)</f>
+        <v/>
+      </c>
+      <c r="N26" s="11" t="n">
+        <f aca="false">IF(K26="",L26,L26+M26)</f>
+        <v>7500</v>
+      </c>
+      <c r="O26" s="8"/>
+      <c r="P26" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" s="12"/>
+      <c r="L27" s="10" t="n">
+        <f aca="false">I27*J27</f>
+        <v>9600</v>
+      </c>
+      <c r="M27" s="10" t="str">
+        <f aca="false">IF(K27="","",K27*12*J27)</f>
+        <v/>
+      </c>
+      <c r="N27" s="11" t="n">
+        <f aca="false">IF(K27="",L27,L27+M27)</f>
+        <v>9600</v>
+      </c>
+      <c r="O27" s="8"/>
+      <c r="P27" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>4750</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="12"/>
+      <c r="L28" s="10" t="n">
+        <f aca="false">I28*J28</f>
+        <v>9500</v>
+      </c>
+      <c r="M28" s="10" t="str">
+        <f aca="false">IF(K28="","",K28*12*J28)</f>
+        <v/>
+      </c>
+      <c r="N28" s="11" t="n">
+        <f aca="false">IF(K28="",L28,L28+M28)</f>
+        <v>9500</v>
+      </c>
+      <c r="O28" s="8"/>
+      <c r="P28" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="12"/>
+      <c r="L29" s="10" t="n">
+        <f aca="false">I29*J29</f>
+        <v>9000</v>
+      </c>
+      <c r="M29" s="10" t="str">
+        <f aca="false">IF(K29="","",K29*12*J29)</f>
+        <v/>
+      </c>
+      <c r="N29" s="11" t="n">
+        <f aca="false">IF(K29="",L29,L29+M29)</f>
+        <v>9000</v>
+      </c>
+      <c r="O29" s="8"/>
+      <c r="P29" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>2700</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="12"/>
+      <c r="L30" s="10" t="n">
+        <f aca="false">I30*J30</f>
+        <v>5400</v>
+      </c>
+      <c r="M30" s="10" t="str">
+        <f aca="false">IF(K30="","",K30*12*J30)</f>
+        <v/>
+      </c>
+      <c r="N30" s="11" t="n">
+        <f aca="false">IF(K30="",L30,L30+M30)</f>
+        <v>5400</v>
+      </c>
+      <c r="O30" s="8"/>
+      <c r="P30" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>11000</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="12"/>
+      <c r="L31" s="10" t="n">
+        <f aca="false">I31*J31</f>
+        <v>11000</v>
+      </c>
+      <c r="M31" s="10" t="str">
+        <f aca="false">IF(K31="","",K31*12*J31)</f>
+        <v/>
+      </c>
+      <c r="N31" s="11" t="n">
+        <f aca="false">IF(K31="",L31,L31+M31)</f>
+        <v>11000</v>
+      </c>
+      <c r="O31" s="8"/>
+      <c r="P31" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>590</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K32" s="12"/>
+      <c r="L32" s="10" t="n">
+        <f aca="false">I32*J32</f>
+        <v>885</v>
+      </c>
+      <c r="M32" s="10" t="str">
+        <f aca="false">IF(K32="","",K32*12*J32)</f>
+        <v/>
+      </c>
+      <c r="N32" s="11" t="n">
+        <f aca="false">IF(K32="",L32,L32+M32)</f>
+        <v>885</v>
+      </c>
+      <c r="O32" s="8"/>
+      <c r="P32" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>590</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K33" s="12"/>
+      <c r="L33" s="10" t="n">
+        <f aca="false">I33*J33</f>
+        <v>885</v>
+      </c>
+      <c r="M33" s="10" t="str">
+        <f aca="false">IF(K33="","",K33*12*J33)</f>
+        <v/>
+      </c>
+      <c r="N33" s="11" t="n">
+        <f aca="false">IF(K33="",L33,L33+M33)</f>
+        <v>885</v>
+      </c>
+      <c r="O33" s="8"/>
+      <c r="P33" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>656</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="12"/>
+      <c r="L34" s="10" t="n">
+        <f aca="false">I34*J34</f>
+        <v>1312</v>
+      </c>
+      <c r="M34" s="10" t="str">
+        <f aca="false">IF(K34="","",K34*12*J34)</f>
+        <v/>
+      </c>
+      <c r="N34" s="11" t="n">
+        <f aca="false">IF(K34="",L34,L34+M34)</f>
+        <v>1312</v>
+      </c>
+      <c r="O34" s="8"/>
+      <c r="P34" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>11540</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" s="12"/>
+      <c r="L35" s="10" t="n">
+        <f aca="false">I35*J35</f>
+        <v>23080</v>
+      </c>
+      <c r="M35" s="10" t="str">
+        <f aca="false">IF(K35="","",K35*12*J35)</f>
+        <v/>
+      </c>
+      <c r="N35" s="11" t="n">
+        <f aca="false">IF(K35="",L35,L35+M35)</f>
+        <v>23080</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>14600</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>5128</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="12"/>
+      <c r="L36" s="10" t="n">
+        <f aca="false">I36*J36</f>
+        <v>10256</v>
+      </c>
+      <c r="M36" s="10" t="str">
+        <f aca="false">IF(K36="","",K36*12*J36)</f>
+        <v/>
+      </c>
+      <c r="N36" s="11" t="n">
+        <f aca="false">IF(K36="",L36,L36+M36)</f>
+        <v>10256</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>14600</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I37" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="11" t="str">
-        <f aca="false">IF(K20="","",K20*12*J20)</f>
+      <c r="J37" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="12"/>
+      <c r="L37" s="10" t="n">
+        <f aca="false">I37*J37</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="10" t="str">
+        <f aca="false">IF(K37="","",K37*12*J37)</f>
         <v/>
       </c>
-      <c r="N20" s="12" t="n">
-        <f aca="false">IF(K20="",L20,L20+M20)</f>
+      <c r="N37" s="11" t="n">
+        <f aca="false">IF(K37="",L37,L37+M37)</f>
         <v>0</v>
       </c>
-      <c r="O20" s="8"/>
-      <c r="P20" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>112</v>
+      <c r="O37" s="8"/>
+      <c r="P37" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3193,1314 +4221,1314 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>114</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>118</v>
+        <v>177</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>123</v>
+        <v>182</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>124</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>139</v>
+        <v>200</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>90</v>
+        <v>205</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>88</v>
+        <v>207</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>146</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>147</v>
+        <v>210</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>150</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>151</v>
+        <v>214</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>154</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>156</v>
+        <v>219</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>161</v>
+        <v>224</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>162</v>
+        <v>225</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>163</v>
+        <v>226</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>164</v>
+        <v>227</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>168</v>
+        <v>231</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>169</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>170</v>
+        <v>233</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>171</v>
+        <v>234</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>176</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>177</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>184</v>
+        <v>245</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>185</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>190</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>192</v>
+        <v>252</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>197</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>198</v>
+        <v>258</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>199</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>201</v>
+        <v>261</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>203</v>
+        <v>263</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>204</v>
+        <v>264</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>206</v>
+        <v>266</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>208</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>84</v>
+        <v>269</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>88</v>
+        <v>207</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>210</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>212</v>
+        <v>274</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>215</v>
+        <v>277</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="J32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>216</v>
+        <v>278</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>219</v>
+        <v>281</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>222</v>
+        <v>283</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>223</v>
+        <v>284</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>225</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>228</v>
+        <v>289</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>229</v>
+        <v>290</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>230</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>232</v>
+        <v>98</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>233</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>236</v>
+        <v>296</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>237</v>
+        <v>297</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>238</v>
+        <v>298</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>239</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>241</v>
+        <v>301</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>242</v>
+        <v>302</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>244</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>246</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>247</v>
+        <v>307</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>248</v>
+        <v>308</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>253</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>256</v>
+        <v>316</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>257</v>
+        <v>317</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>258</v>
+        <v>318</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>259</v>
+        <v>319</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>261</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -4533,444 +5561,444 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>265</v>
+        <v>325</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>266</v>
+        <v>326</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>267</v>
+        <v>327</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>268</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>269</v>
+        <v>329</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>271</v>
+        <v>331</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>272</v>
+        <v>332</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>273</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>274</v>
+        <v>334</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>275</v>
+        <v>335</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>276</v>
+        <v>336</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>277</v>
+        <v>337</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>273</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>278</v>
+        <v>338</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>281</v>
+        <v>341</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>282</v>
+        <v>342</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>273</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>283</v>
+        <v>343</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>286</v>
+        <v>346</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>287</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>288</v>
+        <v>348</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>289</v>
+        <v>349</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>291</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>292</v>
+        <v>352</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>293</v>
+        <v>353</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>294</v>
+        <v>354</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>295</v>
+        <v>355</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>296</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>291</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>301</v>
+        <v>361</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>302</v>
+        <v>362</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>291</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>303</v>
+        <v>363</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>306</v>
+        <v>366</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>307</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>308</v>
+        <v>368</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>249</v>
-      </c>
       <c r="G13" s="6" t="s">
-        <v>307</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>311</v>
+        <v>371</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>312</v>
+        <v>372</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>313</v>
+        <v>373</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>314</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>315</v>
+        <v>57</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>316</v>
+        <v>375</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>317</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>163</v>
+        <v>226</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>319</v>
+        <v>378</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>321</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>306</v>
+        <v>366</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>329</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>330</v>
+        <v>53</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>331</v>
+        <v>389</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>332</v>
+        <v>390</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>333</v>
+        <v>391</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>335</v>
+        <v>393</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>336</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>337</v>
+        <v>395</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>338</v>
+        <v>396</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>339</v>
+        <v>397</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>340</v>
+        <v>398</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>341</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -5003,472 +6031,472 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>343</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>344</v>
+        <v>402</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>345</v>
+        <v>403</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>346</v>
+        <v>404</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>347</v>
+        <v>405</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>349</v>
+        <v>407</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>350</v>
+        <v>408</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>351</v>
+        <v>409</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>352</v>
+        <v>410</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>353</v>
+        <v>411</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>355</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>356</v>
+        <v>414</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>357</v>
+        <v>415</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>359</v>
+        <v>417</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>361</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>362</v>
+        <v>420</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>364</v>
+        <v>422</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>365</v>
+        <v>423</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>294</v>
+        <v>354</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>366</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>367</v>
+        <v>425</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>368</v>
+        <v>426</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>315</v>
+        <v>57</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>369</v>
+        <v>427</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>371</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>372</v>
+        <v>430</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>373</v>
+        <v>431</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>374</v>
+        <v>432</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>375</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>376</v>
+        <v>434</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>377</v>
+        <v>435</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>315</v>
+        <v>57</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>378</v>
+        <v>436</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>379</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>376</v>
+        <v>434</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>380</v>
+        <v>438</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>381</v>
+        <v>439</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>382</v>
+        <v>440</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>383</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>385</v>
+        <v>443</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>364</v>
+        <v>422</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>294</v>
+        <v>354</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>387</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>388</v>
+        <v>446</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>389</v>
+        <v>447</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>364</v>
+        <v>422</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>390</v>
+        <v>448</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>391</v>
+        <v>449</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>392</v>
+        <v>450</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>394</v>
+        <v>452</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>395</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>396</v>
+        <v>454</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>397</v>
+        <v>455</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>398</v>
+        <v>456</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>399</v>
+        <v>457</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>400</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>401</v>
+        <v>459</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>402</v>
+        <v>460</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>403</v>
+        <v>461</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>404</v>
+        <v>462</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>405</v>
+        <v>463</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>406</v>
+        <v>464</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>407</v>
+        <v>465</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>408</v>
+        <v>466</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>409</v>
+        <v>467</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>410</v>
+        <v>468</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>411</v>
+        <v>469</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>354</v>
-      </c>
       <c r="G18" s="6" t="s">
-        <v>413</v>
+        <v>471</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>414</v>
+        <v>472</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>415</v>
+        <v>473</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>416</v>
+        <v>474</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>382</v>
+        <v>440</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>417</v>
+        <v>475</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>418</v>
+        <v>476</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>419</v>
+        <v>477</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>420</v>
+        <v>478</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>382</v>
+        <v>440</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>421</v>
+        <v>479</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>422</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>423</v>
+        <v>481</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>424</v>
+        <v>482</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="3" t="s">
-        <v>425</v>
+        <v>483</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>426</v>
+        <v>484</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>427</v>
+        <v>485</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>428</v>
+        <v>486</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>429</v>
+        <v>487</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>430</v>
+        <v>488</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="3" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>432</v>
+        <v>490</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="3" t="s">
-        <v>433</v>
+        <v>491</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>434</v>
+        <v>492</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="3" t="s">
-        <v>435</v>
+        <v>493</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>436</v>
+        <v>494</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>437</v>
+        <v>495</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>438</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -5497,236 +6525,236 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>439</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>344</v>
+        <v>402</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>441</v>
+        <v>499</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>442</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>443</v>
+        <v>501</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>444</v>
+        <v>502</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>445</v>
+        <v>503</v>
       </c>
       <c r="D4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>443</v>
+        <v>501</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>446</v>
+        <v>504</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>447</v>
+        <v>505</v>
       </c>
       <c r="D5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>443</v>
+        <v>501</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>448</v>
+        <v>506</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>449</v>
+        <v>507</v>
       </c>
       <c r="D6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>443</v>
+        <v>501</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>450</v>
+        <v>508</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>451</v>
+        <v>509</v>
       </c>
       <c r="D7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>443</v>
+        <v>501</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>452</v>
+        <v>510</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>453</v>
+        <v>511</v>
       </c>
       <c r="D8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>454</v>
+        <v>512</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>456</v>
+        <v>514</v>
       </c>
       <c r="D9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>454</v>
+        <v>512</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>458</v>
+        <v>516</v>
       </c>
       <c r="D10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>454</v>
+        <v>512</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>459</v>
+        <v>517</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>460</v>
+        <v>518</v>
       </c>
       <c r="D11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>461</v>
+        <v>519</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>462</v>
+        <v>520</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>463</v>
+        <v>521</v>
       </c>
       <c r="D12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>461</v>
+        <v>519</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>464</v>
+        <v>522</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>465</v>
+        <v>523</v>
       </c>
       <c r="D13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>466</v>
+        <v>524</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>467</v>
+        <v>525</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>468</v>
+        <v>526</v>
       </c>
       <c r="D14" s="16"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>466</v>
+        <v>524</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>469</v>
+        <v>527</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>470</v>
+        <v>528</v>
       </c>
       <c r="D15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>471</v>
+        <v>529</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>472</v>
+        <v>530</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>473</v>
+        <v>531</v>
       </c>
       <c r="D16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>393</v>
+        <v>451</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>475</v>
+        <v>533</v>
       </c>
       <c r="D17" s="16"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>476</v>
+        <v>534</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>477</v>
+        <v>535</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>478</v>
+        <v>536</v>
       </c>
       <c r="D18" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>479</v>
+        <v>537</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>480</v>
+        <v>538</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>481</v>
+        <v>539</v>
       </c>
       <c r="D19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>482</v>
+        <v>540</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>483</v>
+        <v>541</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>484</v>
+        <v>542</v>
       </c>
       <c r="D20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>485</v>
+        <v>543</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>486</v>
+        <v>544</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>487</v>
+        <v>545</v>
       </c>
       <c r="D21" s="16"/>
     </row>
@@ -5755,175 +6783,175 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>488</v>
+        <v>546</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>489</v>
+        <v>547</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>490</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>491</v>
+        <v>549</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>492</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>493</v>
+        <v>551</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>494</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>495</v>
+        <v>553</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>496</v>
+        <v>554</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>497</v>
+        <v>555</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>498</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>499</v>
+        <v>557</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>500</v>
+        <v>558</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>501</v>
+        <v>559</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>502</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>503</v>
+        <v>561</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>504</v>
+        <v>562</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>505</v>
+        <v>563</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>506</v>
+        <v>564</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>507</v>
+        <v>565</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>508</v>
+        <v>566</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>509</v>
+        <v>567</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>510</v>
+        <v>568</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>511</v>
+        <v>569</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>512</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>513</v>
+        <v>571</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>514</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>515</v>
+        <v>573</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>516</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>517</v>
+        <v>575</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>518</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>519</v>
+        <v>577</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>520</v>
+        <v>578</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>521</v>
+        <v>579</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>522</v>
+        <v>580</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>523</v>
+        <v>581</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>524</v>
+        <v>582</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>339</v>
+        <v>397</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>525</v>
+        <v>583</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>526</v>
+        <v>584</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>527</v>
+        <v>585</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>528</v>
+        <v>586</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>529</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>

--- a/output/masters-research.xlsx
+++ b/output/masters-research.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="770">
   <si>
     <t xml:space="preserve">European Master's Research — Results</t>
   </si>
@@ -568,58 +568,172 @@
     <t xml:space="preserve">D1 AI/data marketing</t>
   </si>
   <si>
+    <t xml:space="preserve">Public (AACSB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "bachelor in economics and management, or related field", no credit count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOP PICK. No English test, no written exam. EUR 10,000 scholarship ranked on SAT alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - no grade requirement published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closes the credit gap in writing: 180-credit holders take 30 more via a 3rd-semester placement. IELTS 6.0. 35 places, grade-weighted ranking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 88/sem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "open to all who pass the aptitude procedure"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French A2 required - he is native. Dual degree with Toulouse. 10 places</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA Entrepreneurship and Digital Transformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HM Munchen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 97/sem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - no grade bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selected on project description + 2-minute pitch video + interview</t>
+  </si>
+  <si>
     <t xml:space="preserve">Applied sciences</t>
   </si>
   <si>
-    <t xml:space="preserve">727/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY OK — 30 ECTS business subjects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free prep course for maths prerequisite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data-Driven Marketing, Digital Mktg &amp; Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,500 total</t>
+    <t xml:space="preserve">EUR 727/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - 30 ECTS business subjects, no 180 rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free video prep course for the maths prerequisite. IELTS 6.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing and Global Markets (LM-77 R)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 346/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "Bachelor diploma (or higher)"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytics inside a marketing degree. Separate earlier non-EU visa round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 390/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest no-paperwork route in Italy (flat income-band rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 400/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "other qualification obtained abroad recognized as suitable"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO ENGLISH TEST - B2 satisfied by 6 ECTS of English in the bachelor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public (AMBA/AACSB/MAB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 7,400/yr or EUR 0 on SH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - needs only 5 ECTS in listed subject areas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO ENGLISH CERTIFICATE - assessed in its own entrance exam. Strongest 146 verdict found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BGE Budapest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 6,600/yr or EUR 0 on SH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IELTS 5.5 / Duolingo 95 - lowest test bar found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 4,800/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - entry by field, not credits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IELTS 6.0. Analytics for Business double degree with Ghent. Non-EU waivers abolished 2026/27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 7,450/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - free binding national assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~15 fully funded awards by AUTOMATIC consideration. Non-EU deadline 15 Jan, not 1 Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 5,128/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - Norway assesses by years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best price-to-match ratio found. BUT see Norway funds trap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Business Administration (Business Analytics)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 4,975/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest Norwegian. 30-ECTS quantitative floor + C-average. Deadline 1 Dec 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 5,385/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No UiA scholarships at all for 2026/27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 7,500 total</t>
   </si>
   <si>
     <t xml:space="preserve">2027/28 applications open soon</t>
   </si>
   <si>
-    <t xml:space="preserve">MSc Econ &amp; Business Admin (Business Data Science)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,450/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~15 fully funded awards, automatic consideration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Business</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,385/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY OK — assessed by years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheapest verified tuition in report</t>
-  </si>
-  <si>
     <t xml:space="preserve">Business &amp; Digital Analytics</t>
   </si>
   <si>
     <t xml:space="preserve">Uniwersytet Lodzki</t>
   </si>
   <si>
-    <t xml:space="preserve">2,500/yr</t>
+    <t xml:space="preserve">EUR 2,500/yr</t>
   </si>
   <si>
     <t xml:space="preserve">Advanced Analytics / Big Data</t>
@@ -628,10 +742,10 @@
     <t xml:space="preserve">SGH Warsaw</t>
   </si>
   <si>
-    <t xml:space="preserve">4,600/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland's leading business school</t>
+    <t xml:space="preserve">EUR 4,600/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland leading business school</t>
   </si>
   <si>
     <t xml:space="preserve">Economic Data Analysis</t>
@@ -640,7 +754,7 @@
     <t xml:space="preserve">VSE Prague</t>
   </si>
   <si>
-    <t xml:space="preserve">6,000/yr</t>
+    <t xml:space="preserve">EUR 6,000/yr</t>
   </si>
   <si>
     <t xml:space="preserve">International Strategic Marketing</t>
@@ -649,172 +763,427 @@
     <t xml:space="preserve">ULiege / HEC Liege</t>
   </si>
   <si>
+    <t xml:space="preserve">French + English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 5,369/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORDERLINE - publishes minimum 12/20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRENCH TEST EXEMPTION VERIFIED. He clears 12/20 by nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Business Administration (Brussels)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KU Leuven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;= EUR 9,494/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - qualitative entry wording</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 ECTS. Preparatory programme with no visa complication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Artificial Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 11,000 net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORDERLINE - Ireland wants NFQ Level 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOMATIC EUR 2,500 award, not competitive. 24 months post-study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Business Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATU Sligo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 14,000/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published RPL route</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 4,500/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closest title match to his CRM project. But Bucharest recruits in RO/EN/DE, not French</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Marketing and Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UEF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 7,000 net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True D1+D2 hybrid. Finland: full-cost tuition law from 1 Aug 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Driven Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUAS Amsterdam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 10,648/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPENDS on licence type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if diploma says Licence Appliquee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDSI - Service Design Strategies &amp; Innovations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 0 if funded (EUR 8,000 if not)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No GPA floor, IELTS 5.5, 5 places reserved for countries incl. Tunisia. CRM build IS service design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUMIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universidad de Sevilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 886 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - licence on the preferred list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~4.3 applicants per place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing y Comportamiento del Consumidor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGR + UJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demands DELE B2 AND English B1 - two certificates he lacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 656/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "titolo equipollente conseguito all estero"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus EDISU Piemonte EUR 8,097 - richest regional grant in Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trade e Consumer Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universita di Parma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISEE-scaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contains Loyalty Marketing and CRM module (10 CFU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LM-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIMORE Reggio Emilia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 159.67/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - OPEN ADMISSION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowest bar in Italy: listed bachelor OR just 30 ECTS in relevant subjects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mestrado em Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.Porto FEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portuguese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 5,000/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eduniversal 14th W. Europe. Marketing Relacional module is literally CRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing e Comunicacao Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universidade de Aveiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 4,150/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/25 rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marqueting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAB Barcelona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish/Catalan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalonia rates (EUR 19.37/cr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalonia decree: study permit does NOT exempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intelligenza Artificiale, Impresa e Societa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IULM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT VERIFIED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2 Digital marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - 30 ECTS business, no 180 rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IELTS 6.0 required (MOI letter will NOT work - must attest English). Deadline 3 March</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 4,055/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - M1 from Licence Economie et Gestion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEST CRM MATCH IN FRANCE. M2 tracks: CRM et Data Marketing, IA et digital Marketing. Eduniversal #3, 83% at 6 months, 24 places</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO ENTRANCE EXAM, B1 minimum. Data analytics, social, UX, influence marketing. Best content-per-euro in Benelux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "licence ou equivalent (180 credits)"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trains "specialistes de la relation client". SIM/TAGE MAGE/GMAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 Marketing, Vente -&gt; Marketing digital (MCD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Metz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "Bac+3 (180 ECTS)"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO Score IAE-Message - dossier + interview only. Lowest French barrier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing Strategique / Marketing et Communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Bordeaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - M1 from "licence generale"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apprenticeship confined to M2 - best structure: FI entry, funded year 2 once permit held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc 1 Management -&gt; MSc 2 Marketing &amp; Brand Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Aix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 8,400 / 2 yrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - admits bac+3 "or credits"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most 146-friendly wording found in France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "grade Licence (180 ECTS)"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORMATION INITIALE ONLY - no alternance pathway. Cleanest file. SIM before March deadline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing et Strategie d Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Saint-Etienne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Format Initiale only, no alternance at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing Digital (MKT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - M1, 180 ECTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entry test has NO eliminating minimum + jury interview. Nice priciest non-Paris city (~EUR 1,370/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public (AACSB+EQUIS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 254 + CVEC, or EUR 4,055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diplome national de master. THE BENCHMARK private schools must beat. Needs English B2 AND DELF/DALF B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decisions marketing operationnelles et digitales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Amiens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FI cohort proven. SEA/SMO, data marketing, AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grenoble IAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three digital M2 exits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 e-Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Montpellier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File + oral interview where the CRM project lands. City has FREE public transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing Operationnel International (parcours classique)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris Nanterre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FI and apprenticeship are separate parcours</t>
+  </si>
+  <si>
     <t xml:space="preserve">French/English</t>
   </si>
   <si>
-    <t xml:space="preserve">5,369/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publishes a minimum 12/20 average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc Artificial Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11,000 net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BORDERLINE — wants NFQ L8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automatic EUR 2,500 award</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc Business Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATU Sligo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,000/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Published RPL route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital Driven Business</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUAS Amsterdam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netherlands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,648/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEPENDS on licence type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only if Licence Appliquee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital Marketing and Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UEF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~7,000 net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">True D1+D2 hybrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketing y Comportamiento del Consumidor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UGR / UJA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~1,300 total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andalucia rates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marqueting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UAB Barcelona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spanish/Catalan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalonia rates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2 Digital marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY OK — no 180 ECTS rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOP PICK. Deadline 3 Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B2 English via free in-house test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~2,700/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entry names marketing as qualifying</t>
+    <t xml:space="preserve">NO LANGUAGE TEST REQUESTED. Official 120-ECTS Belgian master. Long year-2 internship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "minimum 3 years of HE AND/OR 180 credits"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISJUNCTIVE - friendliest wording found anywhere. 6-year diploma-recency rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master 120 sciences de gestion / ingenieur de gestion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNamur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 March deadline for visa applicants. NO ENIC-NARIC equivalence needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2 English met by UW own FREE online test. Entry is a subject test, not GPA ranking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 2,700/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - entry names marketing as qualifying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrance task: prepared presentation + essay. Recognition EUR 39. Deadline 31 May</t>
   </si>
   <si>
     <t xml:space="preserve">MERCURI (customer relationship marketing)</t>
   </si>
   <si>
-    <t xml:space="preserve">UE Katowice + 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,150 total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Literally demands 180 ECTS. Closest to his CRM project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,055/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trains "specialistes de la relation client"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1 Marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formation initiale only — no alternance trap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc 1 Management -&gt; MSc 2 Marketing &amp; Brand Mgmt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAE Aix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,400 / 2yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admits bac+3 "or credits" — best wording found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketing Digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAE Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entry test has no eliminating minimum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenoble IAE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Three digital M2 exits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1 e-Marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAE Montpellier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free public transport in city</t>
+    <t xml:space="preserve">UE Katowice + 3 countries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 5,150 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORDERLINE - literally demands "6 semesters and 180 ECTS"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triple diploma. Closest to his CRM project of the Polish options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 9,500 TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - admits Third Class/Category III with experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IELTS 6.5. iGaming/fintech recruit in English; French an asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc Experiential Digital Marketing Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyprus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same fee regardless of nationality. BUT Cyprus applies a labour market test - cheap qualification, not a route to work</t>
   </si>
   <si>
     <t xml:space="preserve">MSc Strategic Digital Marketing</t>
@@ -829,22 +1198,106 @@
     <t xml:space="preserve">GBP 11,800</t>
   </si>
   <si>
-    <t xml:space="preserve">LIKELY OK — no ECTS rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">February intake available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master en gestion de l'entreprise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICHEC Brussels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No language test requested</t>
+    <t xml:space="preserve">LIKELY OK - UK has no ECTS rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entry 2:2 - he clears it. FEBRUARY INTAKE. Graduate Route now 18 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing &amp; Integrated Communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vilnius University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 5,460/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60% GPA threshold, but IELTS 6.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UL Ljubljana SEB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 4,700/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORDERLINE - explicit 180 ECTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triple Crown accredited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILTEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NHL Stenden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 11,995/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nearest Dutch equivalent to events/entertainment marketing. Deadline 31 May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consultancy &amp; Entrepreneurship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rotterdam UAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 14,449/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admits business bachelors with NO work experience. IELTS 6.5, 1 April</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Marketing &amp; CX Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IESEG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private (triple crown)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 9,810/yr after early bird</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 21,800 whole 120-ECTS degree. GMAT optional. BLOCKER: IELTS 6.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-year track (AI x marketing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EM Normandie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 10,400-11,960/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only AI x marketing hybrid at a triple-crown school. 10%+10% discount stack allowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 886 TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEST WEIGHTING FOUND: 35% academic record / 35% professional experience. No language certificate published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 886-900 TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 ECTS. 99% Andalusian bonificacion should zero year 2. Foreign-student enrolment phase early July</t>
   </si>
   <si>
     <t xml:space="preserve">Digital Marketing (LM-77)</t>
@@ -853,28 +1306,7 @@
     <t xml:space="preserve">Universita di Salerno</t>
   </si>
   <si>
-    <t xml:space="preserve">ISEE-scaled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publicite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHECS Brussels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~1,296 total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHEAPEST state master found. File authorisation by 1 Nov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LM-59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIMORE Reggio Emilia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open admission — only 30 ECTS bar</t>
+    <t xml:space="preserve">CORRECTION: requires Italian B1 from ALL applicants incl. English curriculum - Tier B not A</t>
   </si>
   <si>
     <t xml:space="preserve">Comunicacion Digital</t>
@@ -883,7 +1315,7 @@
     <t xml:space="preserve">Universidad de Alicante</t>
   </si>
   <si>
-    <t xml:space="preserve">Valencia rates</t>
+    <t xml:space="preserve">Valencia rates (x2 for non-EU)</t>
   </si>
   <si>
     <t xml:space="preserve">Partly blended</t>
@@ -898,430 +1330,544 @@
     <t xml:space="preserve">Czech</t>
   </si>
   <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free, but not recommended — see funding notes</t>
+    <t xml:space="preserve">Free, but prep year costs EUR 7,167 + a lost year. NOT RECOMMENDED</t>
   </si>
   <si>
     <t xml:space="preserve">D3 Music marketing</t>
   </si>
   <si>
-    <t xml:space="preserve">Best route in this direction. M1 entry from L3 gestion</t>
+    <t xml:space="preserve">M1 Management de l innovation -&gt; M2 Management Carrieres d Artistes / Ecosysteme de la Musique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - M1 from "L3 economie et/ou gestion", no credit numeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE ONLY REAL ROUTE IN THIS DIRECTION. Sidesteps France M2-only trap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creative Management in New Media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Silesia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 3,080/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARD FAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires arts/media bachelor PLUS portfolio review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D4 Music business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIOCA - Innovation and Organization of Culture and the Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 157.04/yr with ISEE (max 4,080)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "Bachelor in ANY discipline, minimum three-year duration"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTSTANDING. Real laurea magistrale LM-76 in a MANAGEMENT dept. 25 of 50 places reserved for non-EU abroad. No portfolio, no GMAT. CV(40)+interview(60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 11,540/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "a bachelor degree in economics or equivalent"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONLY music-business master he can enter as he stands. No portfolio, no audition. BUT UiA offers no scholarships + Norway funds trap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master en gestion culturelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120 ECTS. No language test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOCA (management route)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVSQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 4,055/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Official licences conseillees list includes "Gestion"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ca Foscari Venezia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 1,300/yr FLAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT VERIFIED (site down)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WARNING: ISEE parificato NOT valid at Ca Foscari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cultural Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAMT / EBS Tallinn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - "any field" entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 scholarships. Case study + interview admission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSc International Music Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rennes School of Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 11,950/yr net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 28,900 total less EUR 5,000 Talent award. RNCP 7 + CGE. STRETCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA Music Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Popakademie Baden-Wurttemberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">German</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 3,000/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIKELY OK - 180 ECTS accepted, no grade bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOCKED by six months creative-sector experience requirement. No C1-German requirement or entrance exam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuition (non-EU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Language for him</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146 issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-study stay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visa funds needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verdict / note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not counted at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOP PICK - no differential non-EU fee exists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 6,600-7,400, EUR 0 if funded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strongest verdict - subject-area minimums only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOP PICK - Tunisia holds 250 SH places, any field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria (right FH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not counted at all in FH law</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 mo -&gt; Red-White-Red Card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOP PICK - but fees range 23-fold across FHs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 0 - 97/sem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credential fine (anabin H+). 23 of 42 set no grade bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 11,904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REOPENED - visa needs unconditional admission certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 157-1,000/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English or Italian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine - "at least three years"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~12 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOP PICK - two fee regimes; Milano Statale is the trap at EUR 3,394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">French - native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine - thinks in "Bac+3"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 mo APS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 14,500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOP PICK - but screen M1 entry AND formation initiale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish (Tier B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine - "3 complete academic years"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 mo, no work rights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest in Europe. Zero English-taught in Andalucia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridging route, 60 complementary credits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 mo, full work rights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMons wording disjunctive. Carry FSEG French-medium attestation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREE binding national assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 yrs but 90 hrs/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aalborg ~15 automatic awards. Non-EU deadline 15 Jan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 11,000-14,000/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borderline - wants NFQ Level 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 mo, full work rights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NARIC Ireland check is free - run it early</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 4,000-7,500/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English or Portuguese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The answer if the family cannot show EUR 14,600 cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 2,500-7,500 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English (B2 now required by law)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine - Lisbon access principle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAWA Banach pays PLN 2,500/mo, Tunisia eligible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 4,800-6,000/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine - entry by field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tartu abolished non-EU waivers 2026/27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 2,700/yr, or 0 in Czech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English or Czech (Tier C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 mo, full access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czech-taught free but prep year costs more than it saves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 9,500 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admits Third Class + experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGaming/fintech hire in English. Re-check ODA list Feb 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASE has an actual CRM master. Recruits in RO/EN/DE, not French</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 7,000-10,000/yr net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 yrs any sector - best in Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 9,600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-cost tuition law 1 Aug 2026; scholarships ended for new fee-liable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBP 11,800-23,000/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does not use ECTS at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 months from Jan 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBP 10,539 held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three institutions wide. NI is NOT cheap: QUB GBP 23,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labour market test applies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheap EU qualification, not a route to work there</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 4,975-5,385/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine - assessed by years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 14,600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSED - no institution offers a grant to satisfy the funds rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 9,000-17,100/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSED - Tunisia not among SI 34 eligible countries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 10,648-14,449/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPENDS which licence he holds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appliquee -&gt; HBO open. Fondamentale -&gt; rated below a Dutch bachelor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English (C2 demanded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOATAP challenges it, no safety valve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSED - C2 English + DOATAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luxembourg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 8,000 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOCKING - "180 ECTS" stated 3x, no fallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSED - no marketing, communication or music master exists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOCKING - "at least 3 years, at least 180 ECTS"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding, by deadline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most 2027/28 calls are not yet open. Dates show when in the year to look.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scheme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it covers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who applies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~Oct 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MESRS pret (loan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tunisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Means-tested loan, 10-yr repayment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worth asking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GRANT is closed to him — see notes below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1 Oct 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eiffel campaign opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 1,200/mo + automatic fee exemption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long-shot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSITY nominates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask the international office in writing, early</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct-Dec 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erasmus Mundus wave opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuition + ~EUR 1,400/mo, max 33,600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~10% cap per nationality — competes vs Tunisians</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~Nov 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stipendium Hungaricum opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuition + dorm + HUF 43,700/mo (~EUR 110)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REALISTIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tunisia holds 250 places, 130 for master's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~8 Jan 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eiffel deposit deadline</t>
   </si>
   <si>
     <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creative Management in New Media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University of Silesia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,080/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARD FAIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs arts bachelor + portfolio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D4 Music business</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIOCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157/yr with ISEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIKELY OK — "any discipline, min 3 years"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 of 50 places reserved for non-EU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11,540/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only music master he can enter as he stands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ca' Foscari Venezia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT VERIFIED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site was down</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master en gestion culturelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No language test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOCA (management route)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVSQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~4,055/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recommended licences list includes "Gestion"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSc International Music Business</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rennes School of Business</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~11,950 net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STRETCH. RNCP 7 + CGE, triple accredited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuition (non-EU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Language for him</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146 issue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-study stay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visa funds needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verdict</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria (right FH)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 727/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not counted at all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 mo -&gt; Red-White-Red Card</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOP PICK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 157-1,000/yr with ISEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English or Italian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fine — "three years"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~12 mo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 4,055/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">French — native</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fine — "Bac+3"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 mo APS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~EUR 14,500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~EUR 1,300 total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spanish (Tier B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fine — "3 years"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 mo, no work rights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strong, later</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 7,450/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free binding assessment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 yrs but 90 hrs/mo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 5,385/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fine — assessed by years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~EUR 14,600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reopened</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 11,000-14,000/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Borderline — wants NFQ L8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 mo, full work rights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 5,369/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridging route exists (60 cr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 mo, full work rights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 4,000-7,500/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English or Portuguese</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~EUR 2,500-7,500 total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English (B2 now required)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 mo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 2,700/yr, or 0 in Czech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English or Czech (Tier C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 mo, full access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 + stipend if funded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One application</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 7,000-10,000/yr net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 yrs any sector — best in Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~EUR 9,600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costlier now</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBP 11,800-23,000/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Does not exist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 months from Jan 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBP 10,539 held</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Three schools only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funding closed to Tunisians</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~0-1,500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">German (Tier C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credential fine; GPA blocks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 mo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 11,904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deprioritise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depends on which licence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depends on diploma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blocked — explicit 180 rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funding, by deadline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Most 2027/28 calls are not yet open. Dates show when in the year to look.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">When</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scheme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What it covers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Who applies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~Oct 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MESRS pret (loan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tunisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Means-tested loan, 10-yr repayment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worth asking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The GRANT is closed to him — see notes below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~1 Oct 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eiffel campaign opens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUR 1,200/mo + automatic fee exemption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long-shot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSITY nominates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask the international office in writing, early</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oct-Dec 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erasmus Mundus wave opens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuition + ~EUR 1,400/mo, max 33,600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~10% cap per nationality — competes vs Tunisians</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~Nov 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stipendium Hungaricum opens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuition + dorm + HUF 43,700/mo (~EUR 110)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REALISTIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tunisia holds 250 places, 130 for master's</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~8 Jan 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eiffel deposit deadline</t>
   </si>
   <si>
     <t xml:space="preserve">University</t>
@@ -4204,7 +4750,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -4261,7 +4807,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
         <v>179</v>
       </c>
@@ -4269,13 +4815,13 @@
         <v>48</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>180</v>
@@ -4293,7 +4839,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>179</v>
       </c>
@@ -4301,31 +4847,31 @@
         <v>48</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>179</v>
       </c>
@@ -4333,28 +4879,28 @@
         <v>48</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>188</v>
+        <v>66</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H7" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4365,16 +4911,16 @@
         <v>48</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>159</v>
+        <v>53</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>49</v>
@@ -4389,7 +4935,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>179</v>
       </c>
@@ -4397,29 +4943,31 @@
         <v>48</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J9" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>179</v>
       </c>
@@ -4427,16 +4975,16 @@
         <v>48</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>199</v>
+        <v>76</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>49</v>
@@ -4445,10 +4993,10 @@
         <v>200</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4459,29 +5007,31 @@
         <v>48</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J11" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
         <v>179</v>
       </c>
@@ -4489,31 +5039,31 @@
         <v>48</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="I12" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="J12" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
         <v>179</v>
       </c>
@@ -4521,31 +5071,31 @@
         <v>48</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>210</v>
+        <v>55</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H13" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
         <v>179</v>
       </c>
@@ -4553,31 +5103,31 @@
         <v>48</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>214</v>
+        <v>55</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
         <v>179</v>
       </c>
@@ -4585,31 +5135,31 @@
         <v>48</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>218</v>
+        <v>124</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>219</v>
+        <v>125</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>220</v>
+        <v>126</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>179</v>
       </c>
@@ -4617,28 +5167,28 @@
         <v>48</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>225</v>
+        <v>113</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>226</v>
+        <v>114</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4646,314 +5196,312 @@
         <v>179</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>229</v>
+        <v>161</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>230</v>
+        <v>162</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>50</v>
+        <v>222</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
         <v>179</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>235</v>
+        <v>49</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="6"/>
+      <c r="J18" s="6" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>69</v>
+        <v>228</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>238</v>
+        <v>50</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>50</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>137</v>
+        <v>234</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J21" s="6" t="s">
-        <v>242</v>
-      </c>
+      <c r="J21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>118</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>89</v>
+        <v>240</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>90</v>
+        <v>241</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="J24" s="6" t="s">
         <v>248</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="I25" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H25" s="6" t="s">
+      <c r="J25" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J25" s="6" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="I26" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>257</v>
@@ -4961,95 +5509,95 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>260</v>
+        <v>132</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>261</v>
+        <v>133</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>50</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>267</v>
+        <v>50</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>268</v>
@@ -5057,7 +5605,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>48</v>
@@ -5069,466 +5617,1780 @@
         <v>270</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>103</v>
+        <v>271</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>271</v>
+        <v>195</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>207</v>
+        <v>49</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>208</v>
+        <v>272</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>105</v>
+        <v>273</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>274</v>
+        <v>165</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>185</v>
+        <v>276</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J31" s="6"/>
+        <v>105</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>271</v>
+        <v>184</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>208</v>
+        <v>281</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="J32" s="6"/>
+        <v>282</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>150</v>
+        <v>284</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>151</v>
+        <v>285</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>146</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>149</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>50</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>280</v>
+        <v>153</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>281</v>
+        <v>154</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>63</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>156</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>50</v>
+        <v>288</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>50</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>287</v>
+        <v>148</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>137</v>
+        <v>295</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>289</v>
+        <v>156</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="I36" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I37" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J36" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="I37" s="13" t="s">
+      <c r="J37" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="I38" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J37" s="13" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="H38" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="I38" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="J38" s="13" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J38" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>300</v>
+        <v>179</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>62</v>
+        <v>309</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>49</v>
+        <v>310</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>303</v>
+        <v>50</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>300</v>
+        <v>179</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>157</v>
+        <v>313</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>158</v>
+        <v>314</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>185</v>
+        <v>315</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>316</v>
+      </c>
+      <c r="J40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>308</v>
+        <v>70</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>275</v>
+        <v>196</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>311</v>
+        <v>84</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>312</v>
+        <v>85</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>208</v>
+        <v>320</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>105</v>
+        <v>321</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>314</v>
+        <v>101</v>
       </c>
       <c r="D43" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>315</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>316</v>
+        <v>246</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="J43" s="6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
-        <v>300</v>
-      </c>
       <c r="B44" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>318</v>
+        <v>89</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>319</v>
+        <v>90</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>86</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>271</v>
+        <v>184</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>320</v>
       </c>
       <c r="I44" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="I49" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J44" s="6" t="s">
-        <v>321</v>
+      <c r="J49" s="6" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -5547,7 +7409,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -5561,7 +7423,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5569,436 +7431,597 @@
         <v>30</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>323</v>
+        <v>480</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>324</v>
+        <v>481</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>325</v>
+        <v>482</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>326</v>
+        <v>483</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>327</v>
+        <v>484</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>329</v>
+        <v>45</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>330</v>
+        <v>181</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>331</v>
+        <v>486</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>332</v>
+        <v>487</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="B8" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="B9" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>142</v>
-      </c>
       <c r="B10" s="6" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>49</v>
+        <v>513</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>358</v>
+        <v>514</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>359</v>
+        <v>515</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
         <v>103</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>360</v>
+        <v>246</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>339</v>
+        <v>508</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>361</v>
+        <v>517</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>362</v>
+        <v>518</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="B14" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="B15" s="6" t="s">
-        <v>375</v>
+        <v>531</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>49</v>
+        <v>532</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>309</v>
+        <v>533</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>309</v>
+        <v>487</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>226</v>
+        <v>126</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>377</v>
+        <v>535</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>365</v>
+        <v>536</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>378</v>
+        <v>491</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>379</v>
+        <v>316</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>265</v>
+        <v>138</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>381</v>
+        <v>538</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>49</v>
+        <v>539</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>382</v>
+        <v>529</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>383</v>
+        <v>540</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>384</v>
+        <v>316</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>386</v>
+        <v>130</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>387</v>
+        <v>542</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>365</v>
+        <v>543</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>366</v>
+        <v>491</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>389</v>
+        <v>262</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>390</v>
+        <v>49</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>391</v>
+        <v>529</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>392</v>
+        <v>491</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>393</v>
+        <v>316</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>294</v>
+        <v>546</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>395</v>
+        <v>529</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>294</v>
+        <v>547</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>294</v>
+        <v>548</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>294</v>
+        <v>550</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>294</v>
+        <v>49</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>398</v>
+        <v>551</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>294</v>
+        <v>552</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>294</v>
+        <v>553</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>399</v>
+        <v>554</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -6031,32 +8054,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>400</v>
+        <v>581</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>401</v>
+        <v>582</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>402</v>
+        <v>583</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>403</v>
+        <v>584</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>404</v>
+        <v>585</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>405</v>
+        <v>586</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>406</v>
+        <v>587</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>178</v>
@@ -6064,439 +8087,439 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>407</v>
+        <v>588</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>408</v>
+        <v>589</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>409</v>
+        <v>590</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>410</v>
+        <v>591</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>411</v>
+        <v>592</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>413</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>414</v>
+        <v>595</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>415</v>
+        <v>596</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>416</v>
+        <v>597</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>417</v>
+        <v>598</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>418</v>
+        <v>599</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>419</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>420</v>
+        <v>601</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>421</v>
+        <v>602</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>422</v>
+        <v>603</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>423</v>
+        <v>604</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>354</v>
+        <v>559</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>424</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>425</v>
+        <v>606</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>426</v>
+        <v>607</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>57</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>427</v>
+        <v>608</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>428</v>
+        <v>609</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>429</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>430</v>
+        <v>611</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>431</v>
+        <v>612</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>294</v>
+        <v>613</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>294</v>
+        <v>613</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>432</v>
+        <v>614</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>433</v>
+        <v>615</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>434</v>
+        <v>616</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>435</v>
+        <v>617</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>57</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>436</v>
+        <v>618</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>428</v>
+        <v>609</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>437</v>
+        <v>619</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>434</v>
+        <v>616</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>438</v>
+        <v>620</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>439</v>
+        <v>621</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>440</v>
+        <v>622</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>441</v>
+        <v>623</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>442</v>
+        <v>624</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>443</v>
+        <v>625</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>422</v>
+        <v>603</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>444</v>
+        <v>626</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>354</v>
+        <v>559</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>445</v>
+        <v>627</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>446</v>
+        <v>628</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>447</v>
+        <v>629</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>422</v>
+        <v>603</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>448</v>
+        <v>630</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>428</v>
+        <v>609</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>449</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>450</v>
+        <v>632</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>451</v>
+        <v>633</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>452</v>
+        <v>634</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>294</v>
+        <v>613</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>453</v>
+        <v>635</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>454</v>
+        <v>636</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>455</v>
+        <v>637</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>63</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>456</v>
+        <v>638</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>457</v>
+        <v>639</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>458</v>
+        <v>640</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>459</v>
+        <v>641</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>460</v>
+        <v>642</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>118</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>461</v>
+        <v>643</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>428</v>
+        <v>609</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>462</v>
+        <v>644</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>463</v>
+        <v>645</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>464</v>
+        <v>646</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>63</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>465</v>
+        <v>647</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>428</v>
+        <v>609</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>466</v>
+        <v>648</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>467</v>
+        <v>649</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>468</v>
+        <v>650</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>146</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>469</v>
+        <v>651</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>470</v>
+        <v>652</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>471</v>
+        <v>653</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>472</v>
+        <v>654</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>473</v>
+        <v>655</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>63</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>474</v>
+        <v>656</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>440</v>
+        <v>622</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>475</v>
+        <v>657</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>476</v>
+        <v>658</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>477</v>
+        <v>659</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>146</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>478</v>
+        <v>660</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>440</v>
+        <v>622</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>479</v>
+        <v>661</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>480</v>
+        <v>662</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>481</v>
+        <v>663</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>482</v>
+        <v>664</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="3" t="s">
-        <v>483</v>
+        <v>665</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>484</v>
+        <v>666</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>485</v>
+        <v>667</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>486</v>
+        <v>668</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>487</v>
+        <v>669</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>488</v>
+        <v>670</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="3" t="s">
-        <v>489</v>
+        <v>671</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>490</v>
+        <v>672</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="3" t="s">
-        <v>491</v>
+        <v>673</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>492</v>
+        <v>674</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="3" t="s">
-        <v>493</v>
+        <v>675</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>494</v>
+        <v>676</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>495</v>
+        <v>677</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>496</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -6525,236 +8548,236 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>497</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>402</v>
+        <v>583</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>498</v>
+        <v>680</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>499</v>
+        <v>681</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>500</v>
+        <v>682</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>501</v>
+        <v>683</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>502</v>
+        <v>684</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>503</v>
+        <v>685</v>
       </c>
       <c r="D4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>501</v>
+        <v>683</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>504</v>
+        <v>686</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>505</v>
+        <v>687</v>
       </c>
       <c r="D5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>501</v>
+        <v>683</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>506</v>
+        <v>688</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>507</v>
+        <v>689</v>
       </c>
       <c r="D6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>501</v>
+        <v>683</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>508</v>
+        <v>690</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>509</v>
+        <v>691</v>
       </c>
       <c r="D7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>501</v>
+        <v>683</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>510</v>
+        <v>692</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>511</v>
+        <v>693</v>
       </c>
       <c r="D8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>512</v>
+        <v>694</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>513</v>
+        <v>695</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>514</v>
+        <v>696</v>
       </c>
       <c r="D9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>512</v>
+        <v>694</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>515</v>
+        <v>697</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>516</v>
+        <v>698</v>
       </c>
       <c r="D10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>512</v>
+        <v>694</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>517</v>
+        <v>699</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>518</v>
+        <v>700</v>
       </c>
       <c r="D11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>519</v>
+        <v>701</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>520</v>
+        <v>702</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>521</v>
+        <v>703</v>
       </c>
       <c r="D12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>519</v>
+        <v>701</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>522</v>
+        <v>704</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>523</v>
+        <v>705</v>
       </c>
       <c r="D13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>524</v>
+        <v>706</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>525</v>
+        <v>707</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>526</v>
+        <v>708</v>
       </c>
       <c r="D14" s="16"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>524</v>
+        <v>706</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>527</v>
+        <v>709</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>528</v>
+        <v>710</v>
       </c>
       <c r="D15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>529</v>
+        <v>711</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>530</v>
+        <v>712</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>531</v>
+        <v>713</v>
       </c>
       <c r="D16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>532</v>
+        <v>714</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>451</v>
+        <v>633</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>533</v>
+        <v>715</v>
       </c>
       <c r="D17" s="16"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>534</v>
+        <v>716</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>535</v>
+        <v>717</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>536</v>
+        <v>718</v>
       </c>
       <c r="D18" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>537</v>
+        <v>719</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>538</v>
+        <v>720</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>539</v>
+        <v>721</v>
       </c>
       <c r="D19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>540</v>
+        <v>722</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>541</v>
+        <v>723</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>542</v>
+        <v>724</v>
       </c>
       <c r="D20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>543</v>
+        <v>725</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>544</v>
+        <v>726</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>545</v>
+        <v>727</v>
       </c>
       <c r="D21" s="16"/>
     </row>
@@ -6783,175 +8806,175 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>546</v>
+        <v>728</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>547</v>
+        <v>729</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>548</v>
+        <v>730</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>549</v>
+        <v>731</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>550</v>
+        <v>732</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>551</v>
+        <v>733</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>552</v>
+        <v>734</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>553</v>
+        <v>735</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>554</v>
+        <v>736</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>555</v>
+        <v>737</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>556</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>557</v>
+        <v>739</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>558</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>559</v>
+        <v>741</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>560</v>
+        <v>742</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>561</v>
+        <v>743</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>562</v>
+        <v>744</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>563</v>
+        <v>745</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>564</v>
+        <v>746</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>565</v>
+        <v>747</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>566</v>
+        <v>748</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>567</v>
+        <v>749</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>568</v>
+        <v>750</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>569</v>
+        <v>751</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>570</v>
+        <v>752</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>571</v>
+        <v>753</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>572</v>
+        <v>754</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>573</v>
+        <v>755</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>574</v>
+        <v>756</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>575</v>
+        <v>757</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>576</v>
+        <v>758</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>577</v>
+        <v>759</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>578</v>
+        <v>760</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>579</v>
+        <v>761</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>580</v>
+        <v>762</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>581</v>
+        <v>763</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>582</v>
+        <v>764</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>397</v>
+        <v>578</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>583</v>
+        <v>765</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>584</v>
+        <v>766</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>585</v>
+        <v>767</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>586</v>
+        <v>768</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>587</v>
+        <v>769</v>
       </c>
     </row>
   </sheetData>

--- a/output/masters-research.xlsx
+++ b/output/masters-research.xlsx
@@ -16,6 +16,10 @@
     <sheet name="Action plan" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Excluded" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'All programmes'!$A$4:$J$85</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Excluded!$A$4:$D$87</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -26,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="922">
   <si>
     <t xml:space="preserve">European Master's Research — Results</t>
   </si>
@@ -2212,31 +2216,463 @@
     <t xml:space="preserve">Missing either costs real money</t>
   </si>
   <si>
-    <t xml:space="preserve">Checked and excluded — so you do not rediscover them</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why excluded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every Italian "music business master" — LUISS BS, Sapienza MMCM, Roma Tre, IULM, 24ORE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All Master di I livello: 1 year, 60-65 CFU. Not a second-cycle degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nearly every Spanish "master en industria musical" — UC3M, IL3-UB, UAM, SAE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formacion permanente / titulo propio. Likely fails the EQF-6 test for Spain's post-study permit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every French Mastere Specialise, without exception</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CGE rules require Bac+5 (or Bac+4 + 3 years). He holds Bac+3. Not a diplome national; confers no grade de master</t>
+    <t xml:space="preserve">Checked and rejected - so you do not rediscover them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every programme or institution the research examined and ruled out, with the reason. This is the other half of the picture: 81 passed the filters, these did not.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Institution / programme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why it was rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH Nurnberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum grade 1.5, plus GMAT 550 for 1.5-2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochschule Pforzheim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum grade 2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THM / Hochschule Mittelhessen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum 2.3, plus 210 ECTS and German B1 - three walls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FH Munster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum grade 2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochschule Bremen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochschule Hof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum grade 2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNU Neu-Ulm (4 programmes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH Koln</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochschule Mainz (2 programmes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochschule Rhine-Waal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OVGU Magdeburg IMME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum 2.9 - the most generous in Germany, and he still misses it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">htw saar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum grade 2.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochschule Bonn-Rhein-Sieg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vergabeverordnung NRW: only 2 places for non-EU, needing CGPA ~1.0-1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-EU quota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCI Innsbruck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 8,250/semester = EUR 16,500/yr - fails the cost filter outright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMC Krems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 6,900/sem, and prints "minimum 180 ECTS lasting at least six semesters" verbatim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost + 180 rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FH Technikum Wien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 3,000/semester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FH Wiener Neustadt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 850/semester, and demands a certificate not an MOI letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WU Wien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires "at least 180 ECTS with 45 ECTS in business administration"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universitat Wien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepts MOI letters only from EU/EEA/CH/UK/US/AU/NZ/CA institutions - structurally excludes Tunisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Lille - SMRC / MBX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free and M1-entry, but requires a signed French apprenticeship contract before enrolment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternance trap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Caen - Digital &amp; Social Media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternance-mandatory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris-Saclay - MRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM-IAE Versailles - MRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Exclusivement en alternance", 24-month contract from M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Montpellier - CSRC (Microsoft, pure CRM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfect CRM fit but alternance-mandatory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Bretagne Sud - Marketing digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Digitalisation de la relation-client" but alternance-mandatory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Angers - digital M2s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1 is fine but both digital M2 exits are alternance-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Orleans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternance-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Brest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Limoges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No marketing master at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing suitable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Pau-Bayonne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International trade only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Perpignan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2-only entry - he has no M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Rouen / Toulon / Paris Cite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excluded on entry route</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2-only / alternance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Valenciennes - MDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambiguous format; institution gave an email address instead of a published rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAE Savoie - Marketing Cursus International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FI with a CRM module, but hard-gated on a TOEIC/IELTS certificate he does not have</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every French Mastere Specialise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGE rules require Bac+5 (or Bac+4 + 3 years). He holds Bac+3. Not a diplome national</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Degree level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESART (advertises a "Mastere Specialise")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not a CGE member; RNCP registration expiring 31 Aug 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accreditation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queen's University Belfast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBP 23,000/yr for international students, against GBP 7,700 for locals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulster University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBP 18,310/yr international</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UK music-business masters generally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBP 16,000-31,900. Only Westminster survives as a stretch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGent - Marketing Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An ADVANCED master requiring a bachelor AND a master, or a 4-year bachelor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hautes ecoles (HELMo, HEPL, HE Vinci, HEH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offer marketing only at bachelor level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flemish hogescholen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Award no business masters at all since the 2013 integratie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THUAS The Hague</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 19,700 - fails cost and one other filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saxion MBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part-time - carries NO student visa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No visa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HvA Applied AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dutch-taught only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Dutch WO masters (if Licence Fondamentale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuffic rates Fondamentale as 2 years of WO - below a Dutch bachelor. Pre-masters capped at 60 EC cannot bridge a full year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utrecht pre-master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bars students who need a residence permit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUISS Business School - music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master di I livello: 1 year, 60-65 CFU. Not a second-cycle degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sapienza MMCM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master di I livello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roma Tre / IULM / 24ORE music masters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint Louis College of Music, Rome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genuinely AFAM-accredited, but its music-business master is still I livello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milano Statale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~EUR 3,394/yr - Tunisia is Group C and ISEE parificato is EXPLICITLY FORBIDDEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coimbra Business School music-industries course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A pos-graduacao, not a master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UC3M music industry master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titulo propio / formacion permanente - EUR 5,900. Likely fails EQF-6 for the post-study permit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IL3-UB / UAM / SAE music masters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titulo propio - not state masters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UC3M Madrid - English marketing master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 13,500 and C1 English required - stretch on both counts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost + English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uniarts Helsinki - MA Music Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfect subject fit; EUR 28,000/yr with a VERIFIED zero-scholarship position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swedish universities generally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 9,000-17,100/yr, and Tunisia is not among the Swedish Institute 34 eligible countries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost + funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Skovde (best Swedish waiver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50% waiver sits on a games/informatics faculty - matches none of his directions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mismatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finnish universities of applied sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Require 2 years of relevant work experience - he has an internship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oslo and Bergen universities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 16,000-32,000/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BI Norwegian Business School</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 13,650/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rome Business School</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awards a Spanish VIU titulo propio, not an Italian degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EU Business School</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany/Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rated H- by Germany anabin. Degrees from Roehampton/Derby/UCAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSBI Berlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awards no German degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMB Barcelona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUNEIZ titulo propio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISEG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNCP titles valid but no grade, no visa, not CGE, no AACSB/EQUIS/AMBA, and bac+5 tracks are alternance-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESSCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires a 4-year bachelor OR 3 years experience - he has neither</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entry</t>
   </si>
   <si>
     <t xml:space="preserve">Berklee Valencia</t>
@@ -2245,97 +2681,121 @@
     <t xml:space="preserve">~EUR 48,000</t>
   </si>
   <si>
-    <t xml:space="preserve">Uniarts Helsinki MA Music Business</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfect subject fit, EUR 28,000/yr, verified zero scholarships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UK music-business master's generally</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBP 16,000-31,900. Only Westminster survives as a stretch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Popakademie, BIMM, Catalyst Berlin, SAE, ICMP, Saint Louis Rome</t>
+    <t xml:space="preserve">Popakademie, BIMM, Catalyst Berlin, SAE, ICMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Various</t>
   </si>
   <si>
     <t xml:space="preserve">Fail on accreditation, price, or both</t>
   </si>
   <si>
-    <t xml:space="preserve">Rome Business School</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awards a Spanish titulo propio, not an Italian degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EU Business School</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rated H- by Germany's anabin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSBI Berlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awards no German degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMB Barcelona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUNEIZ titulo propio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISEG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNCP titles valid but no grade, no visa, not CGE, no AACSB/EQUIS/AMBA, and bac+5 tracks are alternance-only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESSCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires a 4-year bachelor or 3 years' experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All AI/data Erasmus Mundus programmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every one requires a CS, engineering or maths first degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMMIE (Erasmus Mundus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires 240 ECTS — unrecoverable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queen's Belfast (GBP 23,000) and Ulster (GBP 18,310)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern Ireland is not the cheap UK route it appears to be</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finnish universities of applied sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Require 2 years' relevant work experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explicit "at least 3 years, at least 180 ECTS", applied strictly</t>
+    <t xml:space="preserve">Accreditation + cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All AI/data Erasmus Mundus (BDMA, EMAI, DEAI, EDISS, CoDaS, NeuroData, MULTICOM, EMLDS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every one requires a CS, engineering or maths first degree - hard blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMMIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires 240 ECTS - unrecoverable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KTU marketing and big-data masters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuanian-taught only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRU Communication and Digital Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is a BACHELOR, not a master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turiba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only an EUR 3,550 MBA; official page bot-blocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUBG / UNWE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out of range / publishes no English master fee at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost / NOT VERIFIED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUEB and Greek masters generally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Require a C2 English diploma, and DOATAP recognition is where 146 gets challenged with no safety valve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English + credits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Luxembourg - Entrepreneurship &amp; Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">States "BA degree with 180 ECTS" three times with NO complementary-credit fallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Luxembourg - Data Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUR 800/yr but demands linear algebra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prerequisite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Silesia - Creative Management in New Media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires an arts/media bachelor PLUS a portfolio review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portfolio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyprus generally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labour market test - jobs go to Cypriots and EU citizens first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job market</t>
   </si>
   <si>
     <t xml:space="preserve">German Studienkolleg</t>
   </si>
   <si>
-    <t xml:space="preserve">Bachelor entry only — irrelevant to master's applicants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAE Lille, IAE Caen, Paris-Saclay (free M1 routes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Require a signed French apprenticeship contract before enrolment — unobtainable pre-visa</t>
+    <t xml:space="preserve">Bachelor entry only - irrelevant to master applicants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swiss universities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicit "at least 3 years, at least 180 ECTS", applied strictly; HES-SO adds work experience</t>
   </si>
 </sst>
 </file>
@@ -2560,6 +3020,39 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F4E79"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F2F2"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -2621,6 +3114,14 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7394,6 +7895,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:J85"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7401,6 +7903,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8797,11 +9300,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8809,19 +9314,22 @@
         <v>728</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="B3" s="5" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>732</v>
       </c>
     </row>
@@ -8830,39 +9338,69 @@
         <v>733</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>734</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>735</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>738</v>
+        <v>53</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>740</v>
+        <v>53</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>741</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>742</v>
+      <c r="D9" s="6" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8870,7 +9408,13 @@
         <v>743</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>744</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8878,87 +9422,153 @@
         <v>745</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>746</v>
+        <v>53</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>748</v>
+        <v>53</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>750</v>
+        <v>53</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>752</v>
+        <v>53</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>754</v>
+        <v>53</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>756</v>
+        <v>53</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>758</v>
+        <v>53</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>760</v>
+        <v>71</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>761</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>763</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>764</v>
+      <c r="D20" s="6" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>578</v>
+        <v>764</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>765</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8966,18 +9576,927 @@
         <v>766</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>767</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>779</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>793</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="s">
+        <v>828</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>832</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7" t="s">
+        <v>859</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="7" t="s">
+        <v>868</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="7" t="s">
+        <v>871</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="7" t="s">
+        <v>873</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>874</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="7" t="s">
+        <v>875</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>876</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="s">
+        <v>881</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>882</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="7" t="s">
+        <v>883</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>884</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>898</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="7" t="s">
+        <v>899</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="D82" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>769</v>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="7" t="s">
+        <v>914</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="7" t="s">
+        <v>917</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>768</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:D87"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8985,5 +10504,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>